--- a/Labs/Lab08-AandA/Lab08BRubric-Authorization.xlsx
+++ b/Labs/Lab08-AandA/Lab08BRubric-Authorization.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos\CS295N-296N-Repos\CS295N-CourseMaterials\Labs\Lab08-AandA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB8DEE2-7175-4B82-A127-4BDC00000E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A2C4C3-9190-4A3F-9F76-8E8325F5A952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15060" yWindow="4200" windowWidth="15048" windowHeight="12336" activeTab="1" xr2:uid="{30F55907-EC47-624F-8636-FE6181D07E02}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="21">
   <si>
     <t>Possible</t>
   </si>
@@ -96,10 +96,10 @@
     <t>Lab 8B Rubric - Authorization</t>
   </si>
   <si>
-    <t>Great job on the user manager page! I like  the way you handle assigning roles.</t>
-  </si>
-  <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Great job on the user manager page!</t>
   </si>
 </sst>
 </file>
@@ -159,19 +159,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,7 +606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B4A847-4F96-D246-88E5-35AE03F623AE}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.69921875" customWidth="1"/>
@@ -614,12 +617,12 @@
     <col min="6" max="6" width="20.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -629,17 +632,17 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
@@ -649,7 +652,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
@@ -657,17 +660,18 @@
         <v>1</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -677,11 +681,14 @@
       <c r="D7">
         <v>3</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -691,11 +698,14 @@
       <c r="D8">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -705,20 +715,25 @@
       <c r="D9">
         <v>7</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="F9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -728,11 +743,14 @@
       <c r="D12">
         <v>6</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -742,11 +760,14 @@
       <c r="D13">
         <v>3</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -756,11 +777,14 @@
       <c r="D14">
         <v>3</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -770,14 +794,18 @@
       <c r="D15">
         <v>3</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -787,11 +815,14 @@
       <c r="D17">
         <v>4</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -801,11 +832,18 @@
       <c r="D18">
         <v>8</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -817,6 +855,8 @@
         <f>SUM(D7:D18)</f>
         <v>40</v>
       </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="3">
